--- a/grupos/3ALCV - Estadisticos 20241.xlsx
+++ b/grupos/3ALCV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="114">
   <si>
     <t>Materia</t>
   </si>
@@ -182,21 +182,21 @@
     <t>Hernández López Elizabeth</t>
   </si>
   <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -209,55 +209,91 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CUAPIO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GILES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ALMANZA</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>ALMANZA</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>VEGA</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>ESPINOZA</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MONDRAGON</t>
   </si>
   <si>
     <t>PAZ</t>
@@ -266,43 +302,61 @@
     <t>MOLINA</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>REGINA DAYTRI</t>
+  </si>
+  <si>
+    <t>ALEXA YAMILET</t>
+  </si>
+  <si>
+    <t>MIRIAM</t>
+  </si>
+  <si>
+    <t>VANESA BETHSABE</t>
   </si>
   <si>
     <t>RAMSES</t>
   </si>
   <si>
+    <t>FRANCISCO XAVIER</t>
+  </si>
+  <si>
     <t>MARIANA</t>
   </si>
   <si>
+    <t>MARYSOL</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
     <t>ESTEFANIA</t>
   </si>
   <si>
     <t>RAYMUNDO</t>
   </si>
   <si>
+    <t>ANGEL ADRIAN</t>
+  </si>
+  <si>
+    <t>SAMIR</t>
+  </si>
+  <si>
+    <t>AIDE SCARLET</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
     <t>KARINA</t>
-  </si>
-  <si>
-    <t>VANESA BETHSABE</t>
-  </si>
-  <si>
-    <t>REGINA DAYTRI</t>
-  </si>
-  <si>
-    <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>SAMIR</t>
-  </si>
-  <si>
-    <t>AIDE SCARLET</t>
-  </si>
-  <si>
-    <t>KAREN</t>
   </si>
   <si>
     <t>MIREILLE</t>
@@ -851,28 +905,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -899,10 +953,10 @@
         <v>-1</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB4">
         <v>8</v>
@@ -911,10 +965,10 @@
         <v>8</v>
       </c>
       <c r="AD4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF4">
         <v>7</v>
@@ -952,28 +1006,28 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1000,7 +1054,7 @@
         <v>-1</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>8</v>
@@ -1012,7 +1066,7 @@
         <v>9</v>
       </c>
       <c r="AD5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE5">
         <v>5</v>
@@ -1053,28 +1107,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1101,13 +1155,13 @@
         <v>-1</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC6">
         <v>8</v>
@@ -1119,7 +1173,7 @@
         <v>10</v>
       </c>
       <c r="AF6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG6">
         <v>-1</v>
@@ -1154,28 +1208,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1202,10 +1256,10 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB7">
         <v>8</v>
@@ -1217,10 +1271,10 @@
         <v>8</v>
       </c>
       <c r="AE7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG7">
         <v>-1</v>
@@ -1255,28 +1309,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1303,10 +1357,10 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>7</v>
@@ -1318,7 +1372,7 @@
         <v>7</v>
       </c>
       <c r="AE8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF8">
         <v>5</v>
@@ -1356,28 +1410,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1407,7 +1461,7 @@
         <v>9</v>
       </c>
       <c r="AA9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB9">
         <v>7</v>
@@ -1422,7 +1476,7 @@
         <v>9</v>
       </c>
       <c r="AF9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG9">
         <v>-1</v>
@@ -1457,28 +1511,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1505,7 +1559,7 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA10">
         <v>8</v>
@@ -1517,13 +1571,13 @@
         <v>9</v>
       </c>
       <c r="AD10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE10">
         <v>10</v>
       </c>
       <c r="AF10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG10">
         <v>-1</v>
@@ -1558,28 +1612,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1606,10 +1660,10 @@
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB11">
         <v>8</v>
@@ -1621,10 +1675,10 @@
         <v>7</v>
       </c>
       <c r="AE11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG11">
         <v>-1</v>
@@ -1659,28 +1713,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1707,7 +1761,7 @@
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <v>7</v>
@@ -1722,10 +1776,10 @@
         <v>9</v>
       </c>
       <c r="AE12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG12">
         <v>-1</v>
@@ -1760,28 +1814,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1811,7 +1865,7 @@
         <v>8</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB13">
         <v>5</v>
@@ -1820,13 +1874,13 @@
         <v>5</v>
       </c>
       <c r="AD13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG13">
         <v>-1</v>
@@ -1861,28 +1915,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1962,28 +2016,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2010,10 +2064,10 @@
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>5</v>
@@ -2025,10 +2079,10 @@
         <v>5</v>
       </c>
       <c r="AE15">
+        <v>5</v>
+      </c>
+      <c r="AF15">
         <v>6</v>
-      </c>
-      <c r="AF15">
-        <v>5</v>
       </c>
       <c r="AG15">
         <v>-1</v>
@@ -2063,28 +2117,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2111,25 +2165,25 @@
         <v>-1</v>
       </c>
       <c r="Z16">
+        <v>8</v>
+      </c>
+      <c r="AA16">
+        <v>8</v>
+      </c>
+      <c r="AB16">
+        <v>7</v>
+      </c>
+      <c r="AC16">
+        <v>7</v>
+      </c>
+      <c r="AD16">
+        <v>7</v>
+      </c>
+      <c r="AE16">
+        <v>8</v>
+      </c>
+      <c r="AF16">
         <v>6</v>
-      </c>
-      <c r="AA16">
-        <v>7</v>
-      </c>
-      <c r="AB16">
-        <v>7</v>
-      </c>
-      <c r="AC16">
-        <v>6</v>
-      </c>
-      <c r="AD16">
-        <v>7</v>
-      </c>
-      <c r="AE16">
-        <v>5</v>
-      </c>
-      <c r="AF16">
-        <v>5</v>
       </c>
       <c r="AG16">
         <v>-1</v>
@@ -2164,28 +2218,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2212,25 +2266,25 @@
         <v>-1</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA17">
         <v>7</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE17">
         <v>7</v>
       </c>
       <c r="AF17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG17">
         <v>-1</v>
@@ -2265,28 +2319,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2313,25 +2367,25 @@
         <v>-1</v>
       </c>
       <c r="Z18">
+        <v>8</v>
+      </c>
+      <c r="AA18">
+        <v>8</v>
+      </c>
+      <c r="AB18">
+        <v>7</v>
+      </c>
+      <c r="AC18">
+        <v>9</v>
+      </c>
+      <c r="AD18">
+        <v>7</v>
+      </c>
+      <c r="AE18">
+        <v>8</v>
+      </c>
+      <c r="AF18">
         <v>6</v>
-      </c>
-      <c r="AA18">
-        <v>7</v>
-      </c>
-      <c r="AB18">
-        <v>7</v>
-      </c>
-      <c r="AC18">
-        <v>8</v>
-      </c>
-      <c r="AD18">
-        <v>7</v>
-      </c>
-      <c r="AE18">
-        <v>7</v>
-      </c>
-      <c r="AF18">
-        <v>5</v>
       </c>
       <c r="AG18">
         <v>-1</v>
@@ -2366,28 +2420,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2414,7 +2468,7 @@
         <v>-1</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>8</v>
@@ -2423,13 +2477,13 @@
         <v>9</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF19">
         <v>9</v>
@@ -2467,28 +2521,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2515,10 +2569,10 @@
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB20">
         <v>7</v>
@@ -2527,13 +2581,13 @@
         <v>8</v>
       </c>
       <c r="AD20">
+        <v>7</v>
+      </c>
+      <c r="AE20">
+        <v>8</v>
+      </c>
+      <c r="AF20">
         <v>6</v>
-      </c>
-      <c r="AE20">
-        <v>7</v>
-      </c>
-      <c r="AF20">
-        <v>5</v>
       </c>
       <c r="AG20">
         <v>-1</v>
@@ -2568,28 +2622,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2616,25 +2670,25 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>10</v>
       </c>
       <c r="AD21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG21">
         <v>-1</v>
@@ -2669,28 +2723,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2717,7 +2771,7 @@
         <v>-1</v>
       </c>
       <c r="Z22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA22">
         <v>9</v>
@@ -2729,13 +2783,13 @@
         <v>9</v>
       </c>
       <c r="AD22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG22">
         <v>-1</v>
@@ -2770,28 +2824,28 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2821,7 +2875,7 @@
         <v>9</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>8</v>
@@ -2830,13 +2884,13 @@
         <v>9</v>
       </c>
       <c r="AD23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE23">
         <v>9</v>
       </c>
       <c r="AF23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG23">
         <v>-1</v>
@@ -2871,28 +2925,28 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2919,10 +2973,10 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>7</v>
@@ -2931,13 +2985,13 @@
         <v>8</v>
       </c>
       <c r="AD24">
+        <v>7</v>
+      </c>
+      <c r="AE24">
+        <v>8</v>
+      </c>
+      <c r="AF24">
         <v>6</v>
-      </c>
-      <c r="AE24">
-        <v>7</v>
-      </c>
-      <c r="AF24">
-        <v>5</v>
       </c>
       <c r="AG24">
         <v>-1</v>
@@ -2972,28 +3026,28 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -3073,28 +3127,28 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3121,10 +3175,10 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB26">
         <v>7</v>
@@ -3136,10 +3190,10 @@
         <v>8</v>
       </c>
       <c r="AE26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG26">
         <v>-1</v>
@@ -3174,28 +3228,28 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3222,25 +3276,25 @@
         <v>-1</v>
       </c>
       <c r="Z27">
+        <v>8</v>
+      </c>
+      <c r="AA27">
+        <v>8</v>
+      </c>
+      <c r="AB27">
+        <v>7</v>
+      </c>
+      <c r="AC27">
+        <v>8</v>
+      </c>
+      <c r="AD27">
         <v>6</v>
       </c>
-      <c r="AA27">
-        <v>7</v>
-      </c>
-      <c r="AB27">
-        <v>7</v>
-      </c>
-      <c r="AC27">
-        <v>8</v>
-      </c>
-      <c r="AD27">
-        <v>7</v>
-      </c>
       <c r="AE27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG27">
         <v>-1</v>
@@ -3275,28 +3329,28 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3323,10 +3377,10 @@
         <v>-1</v>
       </c>
       <c r="Z28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>8</v>
@@ -3338,10 +3392,10 @@
         <v>7</v>
       </c>
       <c r="AE28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG28">
         <v>-1</v>
@@ -3513,7 +3567,7 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -3522,13 +3576,13 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O4">
         <v>100</v>
       </c>
       <c r="P4">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3537,7 +3591,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="T4">
         <v>100</v>
@@ -3546,13 +3600,13 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="W4">
         <v>100</v>
       </c>
       <c r="X4">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y4">
         <v>100</v>
@@ -3590,7 +3644,7 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -3602,10 +3656,10 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="P5">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3614,7 +3668,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5">
         <v>100</v>
@@ -3626,10 +3680,10 @@
         <v>100</v>
       </c>
       <c r="W5">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="X5">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y5">
         <v>100</v>
@@ -3744,7 +3798,7 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -3768,7 +3822,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="T7">
         <v>100</v>
@@ -3821,7 +3875,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -3833,10 +3887,10 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3845,7 +3899,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -3857,10 +3911,10 @@
         <v>100</v>
       </c>
       <c r="W8">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X8">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Y8">
         <v>100</v>
@@ -3898,7 +3952,7 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -3907,13 +3961,13 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P9">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3922,7 +3976,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -3931,13 +3985,13 @@
         <v>100</v>
       </c>
       <c r="V9">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="W9">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X9">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="Y9">
         <v>100</v>
@@ -3975,7 +4029,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -3987,10 +4041,10 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P10">
-        <v>91.7</v>
+        <v>95.7</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3999,7 +4053,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -4011,10 +4065,10 @@
         <v>100</v>
       </c>
       <c r="W10">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X10">
-        <v>91.7</v>
+        <v>95.7</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -4052,7 +4106,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>80</v>
+        <v>77.3</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -4064,10 +4118,10 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="P11">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4076,7 +4130,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>80</v>
+        <v>77.3</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -4088,10 +4142,10 @@
         <v>100</v>
       </c>
       <c r="W11">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="X11">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y11">
         <v>100</v>
@@ -4129,7 +4183,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -4141,10 +4195,10 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P12">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4153,7 +4207,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -4165,10 +4219,10 @@
         <v>100</v>
       </c>
       <c r="W12">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X12">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y12">
         <v>100</v>
@@ -4206,7 +4260,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -4218,10 +4272,10 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P13">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4230,7 +4284,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -4242,10 +4296,10 @@
         <v>100</v>
       </c>
       <c r="W13">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X13">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -4280,10 +4334,10 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="K14">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4295,7 +4349,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -4304,10 +4358,10 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="S14">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="T14">
         <v>100</v>
@@ -4319,7 +4373,7 @@
         <v>100</v>
       </c>
       <c r="W14">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="X14">
         <v>100</v>
@@ -4360,7 +4414,7 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>85</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -4369,13 +4423,13 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O15">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="P15">
-        <v>91.7</v>
+        <v>95.7</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4384,7 +4438,7 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>85</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15">
         <v>100</v>
@@ -4393,13 +4447,13 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="W15">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="X15">
-        <v>91.7</v>
+        <v>95.7</v>
       </c>
       <c r="Y15">
         <v>100</v>
@@ -4437,7 +4491,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>90</v>
+        <v>79.5</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -4449,10 +4503,10 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P16">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -4461,7 +4515,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>90</v>
+        <v>79.5</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -4473,10 +4527,10 @@
         <v>100</v>
       </c>
       <c r="W16">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X16">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y16">
         <v>100</v>
@@ -4514,7 +4568,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -4526,10 +4580,10 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>88.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="P17">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -4538,7 +4592,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="T17">
         <v>100</v>
@@ -4550,10 +4604,10 @@
         <v>100</v>
       </c>
       <c r="W17">
-        <v>88.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="X17">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y17">
         <v>100</v>
@@ -4591,7 +4645,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -4603,10 +4657,10 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P18">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4615,7 +4669,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -4627,10 +4681,10 @@
         <v>100</v>
       </c>
       <c r="W18">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X18">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y18">
         <v>100</v>
@@ -4668,7 +4722,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -4692,7 +4746,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="T19">
         <v>100</v>
@@ -4745,7 +4799,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -4757,7 +4811,7 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -4769,7 +4823,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -4781,7 +4835,7 @@
         <v>100</v>
       </c>
       <c r="W20">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X20">
         <v>100</v>
@@ -4822,7 +4876,7 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -4831,13 +4885,13 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4846,7 +4900,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -4855,13 +4909,13 @@
         <v>100</v>
       </c>
       <c r="V21">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="W21">
         <v>100</v>
       </c>
       <c r="X21">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y21">
         <v>100</v>
@@ -4899,7 +4953,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -4923,7 +4977,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="T22">
         <v>100</v>
@@ -4976,7 +5030,7 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -4991,7 +5045,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5000,7 +5054,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -5015,7 +5069,7 @@
         <v>100</v>
       </c>
       <c r="X23">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y23">
         <v>100</v>
@@ -5053,7 +5107,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -5065,10 +5119,10 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P24">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -5077,7 +5131,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -5089,10 +5143,10 @@
         <v>100</v>
       </c>
       <c r="W24">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X24">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y24">
         <v>100</v>
@@ -5127,10 +5181,10 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="K25">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -5142,19 +5196,19 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>77.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P25">
-        <v>91.7</v>
+        <v>91.3</v>
       </c>
       <c r="Q25">
         <v>100</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="S25">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="T25">
         <v>100</v>
@@ -5166,10 +5220,10 @@
         <v>100</v>
       </c>
       <c r="W25">
-        <v>77.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X25">
-        <v>91.7</v>
+        <v>91.3</v>
       </c>
       <c r="Y25">
         <v>100</v>
@@ -5207,7 +5261,7 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -5219,10 +5273,10 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P26">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5231,7 +5285,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="T26">
         <v>100</v>
@@ -5243,10 +5297,10 @@
         <v>100</v>
       </c>
       <c r="W26">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X26">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y26">
         <v>100</v>
@@ -5284,7 +5338,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -5296,10 +5350,10 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P27">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5308,7 +5362,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T27">
         <v>100</v>
@@ -5320,10 +5374,10 @@
         <v>100</v>
       </c>
       <c r="W27">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X27">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y27">
         <v>100</v>
@@ -5373,7 +5427,7 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -5397,7 +5451,7 @@
         <v>100</v>
       </c>
       <c r="W28">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X28">
         <v>100</v>
@@ -5498,19 +5552,19 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="G3" s="2">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5530,19 +5584,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="G4" s="2">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5553,7 +5607,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -5562,19 +5616,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="G5" s="2">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5585,7 +5639,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -5594,19 +5648,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G6" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5617,7 +5671,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -5626,19 +5680,19 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G7" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5649,7 +5703,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
@@ -5658,19 +5712,19 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G8" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H8">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5681,7 +5735,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>58</v>
@@ -5702,7 +5756,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -5752,7 +5806,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5784,16 +5838,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920221</v>
+        <v>23330051920222</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -5807,16 +5861,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920221</v>
+        <v>23330051920222</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -5830,16 +5884,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920229</v>
+        <v>23330051920228</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -5853,16 +5907,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920229</v>
+        <v>23330051920228</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -5876,22 +5930,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920245</v>
+        <v>23330051920231</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5899,16 +5953,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920245</v>
+        <v>23330051920231</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -5922,22 +5976,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920247</v>
+        <v>23330051920233</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5945,16 +5999,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920247</v>
+        <v>23330051920233</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -5968,39 +6022,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920267</v>
+        <v>23330051920218</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920267</v>
+        <v>23330051920221</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -6014,16 +6068,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920218</v>
+        <v>23330051920223</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -6037,16 +6091,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920228</v>
+        <v>23330051920229</v>
       </c>
       <c r="B13" t="s">
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -6060,16 +6114,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920335</v>
+        <v>23330051920241</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
@@ -6083,16 +6137,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920318</v>
+        <v>23330051920335</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -6106,16 +6160,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920258</v>
+        <v>23330051920245</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
@@ -6129,16 +6183,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920265</v>
+        <v>23330051920247</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
@@ -6152,16 +6206,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920273</v>
+        <v>23330051920249</v>
       </c>
       <c r="B18" t="s">
         <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E18" t="s">
         <v>12</v>
@@ -6170,6 +6224,167 @@
         <v>51</v>
       </c>
       <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920253</v>
+      </c>
+      <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920318</v>
+      </c>
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920258</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920264</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920265</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920267</v>
+      </c>
+      <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920273</v>
+      </c>
+      <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3ALCV - Estadisticos 20241.xlsx
+++ b/grupos/3ALCV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="83">
   <si>
     <t>Materia</t>
   </si>
@@ -209,6 +209,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
@@ -243,6 +246,9 @@
   </si>
   <si>
     <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>FERNANDA YAMILET</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
@@ -5145,7 +5151,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5177,22 +5183,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920220</v>
+        <v>23330051920271</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5200,22 +5206,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920220</v>
+        <v>23330051920271</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5223,22 +5229,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920236</v>
+        <v>23330051920271</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
         <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5246,7 +5252,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920236</v>
+        <v>23330051920220</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -5255,13 +5261,13 @@
         <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5269,13 +5275,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920222</v>
+        <v>23330051920220</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
         <v>77</v>
@@ -5292,22 +5298,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920228</v>
+        <v>23330051920236</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
         <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5315,22 +5321,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920231</v>
+        <v>23330051920236</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5338,24 +5344,93 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
+        <v>23330051920222</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920228</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920231</v>
+      </c>
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
         <v>23330051920233</v>
       </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
         <v>56</v>
       </c>
-      <c r="G9">
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ALCV - Estadisticos 20241.xlsx
+++ b/grupos/3ALCV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="71">
   <si>
     <t>Materia</t>
   </si>
@@ -173,27 +173,27 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Hernández López Elizabeth</t>
+  </si>
+  <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
-    <t>Hernández López Elizabeth</t>
-  </si>
-  <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
+    <t>Martínez Castillo Columba</t>
   </si>
   <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -218,36 +218,12 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GILES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>MACUIXTLE</t>
   </si>
   <si>
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
     <t>FERNANDA YAMILET</t>
   </si>
   <si>
@@ -255,18 +231,6 @@
   </si>
   <si>
     <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>REGINA DAYTRI</t>
-  </si>
-  <si>
-    <t>ALEXA YAMILET</t>
-  </si>
-  <si>
-    <t>MIRIAM</t>
   </si>
 </sst>
 </file>
@@ -817,13 +781,13 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -832,13 +796,13 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>8</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -906,13 +870,13 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -921,19 +885,19 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>7</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>6</v>
       </c>
       <c r="Z5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA5">
         <v>7</v>
@@ -942,7 +906,7 @@
         <v>5</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -995,13 +959,13 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1010,13 +974,13 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>9</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1084,13 +1048,13 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1099,7 +1063,7 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1173,13 +1137,13 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1188,7 +1152,7 @@
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1209,7 +1173,7 @@
         <v>8</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1262,13 +1226,13 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1277,13 +1241,13 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>9</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1298,7 +1262,7 @@
         <v>9</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1351,13 +1315,13 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1366,7 +1330,7 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1387,7 +1351,7 @@
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1440,13 +1404,13 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1455,19 +1419,19 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>7</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>8</v>
       </c>
       <c r="Z11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>7</v>
@@ -1476,7 +1440,7 @@
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1529,13 +1493,13 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1544,7 +1508,7 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1556,7 +1520,7 @@
         <v>7</v>
       </c>
       <c r="Z12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>9</v>
@@ -1618,13 +1582,13 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1633,7 +1597,7 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1645,7 +1609,7 @@
         <v>5</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>7</v>
@@ -1654,7 +1618,7 @@
         <v>8</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1707,13 +1671,13 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="R14">
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -1722,7 +1686,7 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>5</v>
@@ -1796,13 +1760,13 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -1811,7 +1775,7 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1885,13 +1849,13 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -1900,13 +1864,13 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>8</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -1974,13 +1938,13 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -1989,7 +1953,7 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2001,7 +1965,7 @@
         <v>8</v>
       </c>
       <c r="Z17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>8</v>
@@ -2063,13 +2027,13 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2078,13 +2042,13 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>8</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2099,7 +2063,7 @@
         <v>8</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2152,13 +2116,13 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2167,13 +2131,13 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2241,13 +2205,13 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2256,13 +2220,13 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>7</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2330,13 +2294,13 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -2345,19 +2309,19 @@
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>7</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA21">
         <v>7</v>
@@ -2419,13 +2383,13 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -2434,7 +2398,7 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2455,7 +2419,7 @@
         <v>8</v>
       </c>
       <c r="AC22">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2508,13 +2472,13 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -2523,13 +2487,13 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>9</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2597,13 +2561,13 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -2612,7 +2576,7 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2633,7 +2597,7 @@
         <v>8</v>
       </c>
       <c r="AC24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2686,13 +2650,13 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="R25">
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -2701,7 +2665,7 @@
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -2775,13 +2739,13 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -2790,13 +2754,13 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>8</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2864,13 +2828,13 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>-1</v>
@@ -2879,13 +2843,13 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>8</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2953,13 +2917,13 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>-1</v>
@@ -2968,7 +2932,7 @@
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -3164,7 +3128,7 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -3179,7 +3143,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3202,7 +3166,7 @@
         <v>100</v>
       </c>
       <c r="G5">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>95.8</v>
@@ -3223,7 +3187,7 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="O5">
         <v>97.8</v>
@@ -3232,22 +3196,22 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="T5">
         <v>100</v>
       </c>
       <c r="U5">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="V5">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3368,7 +3332,7 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -3436,7 +3400,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -3451,7 +3415,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="V8">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3504,13 +3468,13 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="R9">
         <v>100</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T9">
         <v>90.59999999999999</v>
@@ -3519,7 +3483,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="V9">
-        <v>95.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3572,7 +3536,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -3587,7 +3551,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="V10">
-        <v>95.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3610,7 +3574,7 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>95.8</v>
@@ -3631,7 +3595,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="O11">
         <v>97.8</v>
@@ -3640,22 +3604,22 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>77.3</v>
+        <v>82.8</v>
       </c>
       <c r="R11">
         <v>100</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="T11">
         <v>100</v>
       </c>
       <c r="U11">
-        <v>81.8</v>
+        <v>100</v>
       </c>
       <c r="V11">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3708,7 +3672,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -3723,7 +3687,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="V12">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3776,7 +3740,7 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -3791,7 +3755,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="V13">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -3844,7 +3808,7 @@
         <v>92.5</v>
       </c>
       <c r="Q14">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -3912,7 +3876,7 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>86.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -3927,7 +3891,7 @@
         <v>81.8</v>
       </c>
       <c r="V15">
-        <v>95.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3980,13 +3944,13 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>79.5</v>
+        <v>81.3</v>
       </c>
       <c r="R16">
         <v>100</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -3995,7 +3959,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="V16">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4048,13 +4012,13 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R17">
         <v>100</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T17">
         <v>100</v>
@@ -4063,7 +4027,7 @@
         <v>84.8</v>
       </c>
       <c r="V17">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4116,13 +4080,13 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>97.7</v>
+        <v>93.8</v>
       </c>
       <c r="R18">
         <v>100</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -4131,7 +4095,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="V18">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4184,7 +4148,7 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4252,7 +4216,7 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -4320,7 +4284,7 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -4335,7 +4299,7 @@
         <v>100</v>
       </c>
       <c r="V21">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4388,7 +4352,7 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -4456,7 +4420,7 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -4471,7 +4435,7 @@
         <v>100</v>
       </c>
       <c r="V23">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4524,13 +4488,13 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="R24">
         <v>100</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -4539,7 +4503,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="V24">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4592,13 +4556,13 @@
         <v>92.5</v>
       </c>
       <c r="Q25">
-        <v>81.8</v>
+        <v>59.4</v>
       </c>
       <c r="R25">
         <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="T25">
         <v>100</v>
@@ -4607,7 +4571,7 @@
         <v>87.90000000000001</v>
       </c>
       <c r="V25">
-        <v>91.3</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -4660,7 +4624,7 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -4675,7 +4639,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="V26">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -4728,13 +4692,13 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T27">
         <v>100</v>
@@ -4743,7 +4707,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="V27">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -4868,7 +4832,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
@@ -4877,19 +4841,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G2" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4900,7 +4864,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
@@ -4921,7 +4885,7 @@
         <v>16</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4932,7 +4896,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -4941,19 +4905,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G4" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4964,7 +4928,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -4973,19 +4937,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4996,7 +4960,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -5005,19 +4969,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5028,7 +4992,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -5049,7 +5013,7 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5060,7 +5024,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
@@ -5069,19 +5033,19 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5151,7 +5115,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5192,13 +5156,13 @@
         <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5215,13 +5179,13 @@
         <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5238,13 +5202,13 @@
         <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5258,16 +5222,16 @@
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5275,162 +5239,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920220</v>
+        <v>23330051920236</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" t="s">
         <v>70</v>
       </c>
-      <c r="D6" t="s">
-        <v>77</v>
-      </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920236</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920236</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920222</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920228</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920231</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920233</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ALCV - Estadisticos 20241.xlsx
+++ b/grupos/3ALCV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="66">
   <si>
     <t>Materia</t>
   </si>
@@ -173,24 +173,24 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>Hernández López Elizabeth</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
@@ -209,28 +209,13 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>FERNANDA YAMILET</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>JHON STEVE</t>
   </si>
 </sst>
 </file>
@@ -784,16 +769,16 @@
         <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>9</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -814,7 +799,7 @@
         <v>8</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>7</v>
@@ -873,16 +858,16 @@
         <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>8</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>7</v>
@@ -903,7 +888,7 @@
         <v>7</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC5">
         <v>6</v>
@@ -962,16 +947,16 @@
         <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -983,7 +968,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>8</v>
@@ -992,7 +977,7 @@
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6">
         <v>7</v>
@@ -1051,16 +1036,16 @@
         <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>9</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -1140,16 +1125,16 @@
         <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1229,16 +1214,16 @@
         <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>8</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -1259,7 +1244,7 @@
         <v>8</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC9">
         <v>6</v>
@@ -1318,16 +1303,16 @@
         <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
         <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1345,10 +1330,10 @@
         <v>9</v>
       </c>
       <c r="AA10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -1407,16 +1392,16 @@
         <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
         <v>7</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -1428,7 +1413,7 @@
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z11">
         <v>8</v>
@@ -1496,16 +1481,16 @@
         <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>8</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -1585,16 +1570,16 @@
         <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1606,7 +1591,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>6</v>
@@ -1615,7 +1600,7 @@
         <v>7</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -1674,16 +1659,16 @@
         <v>3</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1695,16 +1680,16 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>8</v>
       </c>
       <c r="AA14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC14">
         <v>5</v>
@@ -1763,16 +1748,16 @@
         <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>8</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -1784,16 +1769,16 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z15">
         <v>8</v>
       </c>
       <c r="AA15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC15">
         <v>6</v>
@@ -1852,16 +1837,16 @@
         <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>8</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1941,16 +1926,16 @@
         <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>8</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>6</v>
@@ -1968,7 +1953,7 @@
         <v>8</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB17">
         <v>7</v>
@@ -2030,16 +2015,16 @@
         <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>9</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2051,7 +2036,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z18">
         <v>9</v>
@@ -2119,16 +2104,16 @@
         <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
         <v>9</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2140,7 +2125,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -2208,16 +2193,16 @@
         <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>8</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2238,7 +2223,7 @@
         <v>7</v>
       </c>
       <c r="AB20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC20">
         <v>6</v>
@@ -2297,16 +2282,16 @@
         <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>9</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2318,7 +2303,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>9</v>
@@ -2327,7 +2312,7 @@
         <v>7</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -2386,16 +2371,16 @@
         <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>9</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2413,7 +2398,7 @@
         <v>9</v>
       </c>
       <c r="AA22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB22">
         <v>8</v>
@@ -2475,16 +2460,16 @@
         <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
         <v>10</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2502,10 +2487,10 @@
         <v>9</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>8</v>
@@ -2564,16 +2549,16 @@
         <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -2653,16 +2638,16 @@
         <v>3</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
         <v>8</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -2742,16 +2727,16 @@
         <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2763,7 +2748,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z26">
         <v>8</v>
@@ -2831,16 +2816,16 @@
         <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
         <v>8</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -2920,16 +2905,16 @@
         <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>10</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -3137,7 +3122,7 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -3412,7 +3397,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V8">
         <v>98.40000000000001</v>
@@ -3477,10 +3462,10 @@
         <v>99.09999999999999</v>
       </c>
       <c r="T9">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="U9">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V9">
         <v>96.90000000000001</v>
@@ -3548,7 +3533,7 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V10">
         <v>96.90000000000001</v>
@@ -3684,7 +3669,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V12">
         <v>98.40000000000001</v>
@@ -3752,7 +3737,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V13">
         <v>98.40000000000001</v>
@@ -3820,7 +3805,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>81.8</v>
+        <v>87.5</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -3885,10 +3870,10 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="U15">
-        <v>81.8</v>
+        <v>87.5</v>
       </c>
       <c r="V15">
         <v>96.90000000000001</v>
@@ -3956,7 +3941,7 @@
         <v>100</v>
       </c>
       <c r="U16">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V16">
         <v>98.40000000000001</v>
@@ -4024,7 +4009,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>84.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V17">
         <v>98.40000000000001</v>
@@ -4092,7 +4077,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V18">
         <v>98.40000000000001</v>
@@ -4228,7 +4213,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -4293,7 +4278,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -4500,7 +4485,7 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V24">
         <v>98.40000000000001</v>
@@ -4559,7 +4544,7 @@
         <v>59.4</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S25">
         <v>91.09999999999999</v>
@@ -4568,7 +4553,7 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>87.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V25">
         <v>90.59999999999999</v>
@@ -4636,7 +4621,7 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V26">
         <v>98.40000000000001</v>
@@ -4704,7 +4689,7 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V27">
         <v>98.40000000000001</v>
@@ -4772,7 +4757,7 @@
         <v>100</v>
       </c>
       <c r="U28">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -4832,7 +4817,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
@@ -4841,19 +4826,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G2" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4864,7 +4849,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
@@ -4873,19 +4858,19 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G3" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4896,7 +4881,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -4905,19 +4890,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4928,7 +4913,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -4937,19 +4922,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G5" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4960,7 +4945,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -4969,19 +4954,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G6" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4992,7 +4977,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -5001,19 +4986,19 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G7" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5115,7 +5100,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5147,22 +5132,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920271</v>
+        <v>23330051920238</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
         <v>65</v>
       </c>
-      <c r="D2" t="s">
-        <v>68</v>
-      </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5170,22 +5155,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920271</v>
+        <v>23330051920238</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" t="s">
         <v>65</v>
       </c>
-      <c r="D3" t="s">
-        <v>68</v>
-      </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5193,70 +5178,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920271</v>
+        <v>23330051920238</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" t="s">
         <v>65</v>
       </c>
-      <c r="D4" t="s">
-        <v>68</v>
-      </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
         <v>51</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920220</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920236</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ALCV - Estadisticos 20241.xlsx
+++ b/grupos/3ALCV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="66">
   <si>
     <t>Materia</t>
   </si>
@@ -179,16 +179,16 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Hernández López Elizabeth</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
     <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
-    <t>Hernández López Elizabeth</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Flores Ovalle Victor</t>
   </si>
   <si>
     <t>Rivera Serra Alma Lilian</t>
@@ -763,7 +763,7 @@
         <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>6</v>
@@ -852,7 +852,7 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
         <v>6</v>
@@ -941,7 +941,7 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -962,7 +962,7 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1030,7 +1030,7 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1119,7 +1119,7 @@
         <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>6</v>
@@ -1140,7 +1140,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1208,7 +1208,7 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -1229,7 +1229,7 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>6</v>
@@ -1297,7 +1297,7 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1386,7 +1386,7 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>7</v>
@@ -1407,7 +1407,7 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1475,7 +1475,7 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -1564,7 +1564,7 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
         <v>6</v>
@@ -1653,7 +1653,7 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -1674,7 +1674,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1742,7 +1742,7 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
         <v>8</v>
@@ -1763,7 +1763,7 @@
         <v>7</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1831,7 +1831,7 @@
         <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>6</v>
@@ -1920,7 +1920,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>8</v>
@@ -1941,7 +1941,7 @@
         <v>6</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -2009,7 +2009,7 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -2098,7 +2098,7 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
         <v>6</v>
@@ -2119,7 +2119,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2187,7 +2187,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>6</v>
@@ -2208,7 +2208,7 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2276,7 +2276,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>9</v>
@@ -2297,7 +2297,7 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2365,7 +2365,7 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -2454,7 +2454,7 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>6</v>
@@ -2543,7 +2543,7 @@
         <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
         <v>6</v>
@@ -2632,7 +2632,7 @@
         <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -2721,7 +2721,7 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>6</v>
@@ -2810,7 +2810,7 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>6</v>
@@ -2899,7 +2899,7 @@
         <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>8</v>
@@ -3790,7 +3790,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q14">
         <v>87.5</v>
@@ -4538,7 +4538,7 @@
         <v>91.3</v>
       </c>
       <c r="P25">
-        <v>92.5</v>
+        <v>81.3</v>
       </c>
       <c r="Q25">
         <v>59.4</v>
@@ -4881,7 +4881,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -4890,19 +4890,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4913,7 +4913,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -4934,7 +4934,7 @@
         <v>4</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4945,7 +4945,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -4998,7 +4998,7 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5100,7 +5100,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5144,10 +5144,10 @@
         <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5167,35 +5167,12 @@
         <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920238</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4">
         <v>5</v>
       </c>
     </row>
